--- a/onlineCompcorImplementation/results/kscDatasetMean.xlsx
+++ b/onlineCompcorImplementation/results/kscDatasetMean.xlsx
@@ -463,7 +463,7 @@
         <v>0.00301287758230595</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004435518550524204</v>
+        <v>0.004435518550524203</v>
       </c>
       <c r="D2" t="n">
         <v>2.049684094425854</v>
@@ -575,7 +575,7 @@
         <v>0.3339627919373828</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5985144769949927</v>
+        <v>0.5985144769949928</v>
       </c>
     </row>
     <row r="7">
